--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,48 +896,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104000075</v>
+        <v>136859212</v>
       </c>
       <c r="B4" t="n">
-        <v>93213</v>
+        <v>92545</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storflobäcken, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545940</v>
+        <v>546001</v>
       </c>
       <c r="R4" t="n">
-        <v>6960315</v>
+        <v>6960304</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -961,22 +961,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,62 +987,53 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000075</t>
+          <t>https://artportalen.se/Sighting/136859212</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104000203</v>
+        <v>104000075</v>
       </c>
       <c r="B5" t="n">
-        <v>93222</v>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1052,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545943</v>
+        <v>545940</v>
       </c>
       <c r="R5" t="n">
-        <v>6960311</v>
+        <v>6960315</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,16 +1123,16 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000203</t>
+          <t>https://artportalen.se/Sighting/104000075</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128369927</v>
+        <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>96565</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1149,38 +1140,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>2812</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>546102</v>
+        <v>546132</v>
       </c>
       <c r="R6" t="n">
-        <v>6960338</v>
+        <v>6960339</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,12 +1194,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,58 +1235,54 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128369927</t>
+          <t>https://artportalen.se/Sighting/136859203</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128369939</v>
+        <v>104000203</v>
       </c>
       <c r="B7" t="n">
-        <v>92869</v>
+        <v>93222</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>3100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(J.C.Schmidt) Baird</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>545954</v>
+        <v>545943</v>
       </c>
       <c r="R7" t="n">
-        <v>6960281</v>
+        <v>6960311</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,12 +1306,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,53 +1332,62 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128369939</t>
+          <t>https://artportalen.se/Sighting/104000203</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128369936</v>
+        <v>128369927</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1389,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>546019</v>
+        <v>546102</v>
       </c>
       <c r="R8" t="n">
-        <v>6960317</v>
+        <v>6960338</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1450,54 +1462,58 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128369936</t>
+          <t>https://artportalen.se/Sighting/128369927</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104000087</v>
+        <v>128369939</v>
       </c>
       <c r="B9" t="n">
-        <v>79946</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storflobäcken, Jmt</t>
+          <t>Gustavsnäs, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>545937</v>
+        <v>545954</v>
       </c>
       <c r="R9" t="n">
-        <v>6960321</v>
+        <v>6960281</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1521,22 +1537,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:07</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:07</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1547,79 +1553,66 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
-        </is>
-      </c>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/104000087</t>
+          <t>https://artportalen.se/Sighting/128369939</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128369934</v>
+        <v>136859207</v>
       </c>
       <c r="B10" t="n">
-        <v>80432</v>
+        <v>93083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>546063</v>
+        <v>546109</v>
       </c>
       <c r="R10" t="n">
-        <v>6960309</v>
+        <v>6960338</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1646,12 +1639,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1677,55 +1680,51 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128369934</t>
+          <t>https://artportalen.se/Sighting/136859207</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128369937</v>
+        <v>136859208</v>
       </c>
       <c r="B11" t="n">
-        <v>99118</v>
+        <v>93083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>546010</v>
+        <v>546101</v>
       </c>
       <c r="R11" t="n">
-        <v>6960306</v>
+        <v>6960330</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1752,17 +1751,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2 blomställningar</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1788,16 +1792,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128369937</t>
+          <t>https://artportalen.se/Sighting/136859208</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128369929</v>
+        <v>136859209</v>
       </c>
       <c r="B12" t="n">
-        <v>104628</v>
+        <v>93083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,38 +1809,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>546099</v>
+        <v>546092</v>
       </c>
       <c r="R12" t="n">
-        <v>6960344</v>
+        <v>6960339</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1863,12 +1863,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>09:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1894,38 +1904,38 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128369929</t>
+          <t>https://artportalen.se/Sighting/136859209</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128369931</v>
+        <v>128369936</v>
       </c>
       <c r="B13" t="n">
-        <v>104628</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222412</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1939,10 +1949,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>546097</v>
+        <v>546019</v>
       </c>
       <c r="R13" t="n">
-        <v>6960325</v>
+        <v>6960317</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2000,58 +2010,54 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128369931</t>
+          <t>https://artportalen.se/Sighting/128369936</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128369932</v>
+        <v>104000087</v>
       </c>
       <c r="B14" t="n">
-        <v>104628</v>
+        <v>79946</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222412</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Storflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>546073</v>
+        <v>545937</v>
       </c>
       <c r="R14" t="n">
-        <v>6960336</v>
+        <v>6960321</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2075,12 +2081,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2091,53 +2107,62 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Annica Berglind</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128369932</t>
+          <t>https://artportalen.se/Sighting/104000087</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128369933</v>
+        <v>128369934</v>
       </c>
       <c r="B15" t="n">
-        <v>104628</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2151,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>546070</v>
+        <v>546063</v>
       </c>
       <c r="R15" t="n">
-        <v>6960317</v>
+        <v>6960309</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2212,16 +2237,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128369933</t>
+          <t>https://artportalen.se/Sighting/128369934</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128369938</v>
+        <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>104628</v>
+        <v>108378</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2229,38 +2254,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222412</v>
+        <v>220083</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>545963</v>
+        <v>546114</v>
       </c>
       <c r="R16" t="n">
-        <v>6960268</v>
+        <v>6960341</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2287,12 +2308,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2318,43 +2349,43 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128369938</t>
+          <t>https://artportalen.se/Sighting/136859201</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128369928</v>
+        <v>128369937</v>
       </c>
       <c r="B17" t="n">
-        <v>101228</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2363,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>546105</v>
+        <v>546010</v>
       </c>
       <c r="R17" t="n">
-        <v>6960345</v>
+        <v>6960306</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2401,6 +2432,11 @@
           <t>2025-09-08</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 blomställningar</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2424,55 +2460,60 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128369928</t>
+          <t>https://artportalen.se/Sighting/128369937</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128369930</v>
+        <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>101228</v>
+        <v>99353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gustavsnäs, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>546104</v>
+        <v>546013</v>
       </c>
       <c r="R18" t="n">
-        <v>6960332</v>
+        <v>6960326</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2499,12 +2540,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2530,54 +2581,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128369930</t>
+          <t>https://artportalen.se/Sighting/136859211</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104000117</v>
+        <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>79917</v>
+        <v>99353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storflobäcken, Jmt</t>
+          <t>Mörtsjön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>545939</v>
+        <v>545979</v>
       </c>
       <c r="R19" t="n">
-        <v>6960325</v>
+        <v>6960300</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2601,22 +2652,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2627,29 +2678,1340 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859214</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128369929</v>
+      </c>
+      <c r="B20" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>546099</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6960344</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369929</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128369931</v>
+      </c>
+      <c r="B21" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>546097</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6960325</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369931</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128369932</v>
+      </c>
+      <c r="B22" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>546073</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6960336</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369932</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128369933</v>
+      </c>
+      <c r="B23" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>546070</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6960317</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369933</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128369938</v>
+      </c>
+      <c r="B24" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>545963</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6960268</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369938</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136859204</v>
+      </c>
+      <c r="B25" t="n">
+        <v>104876</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>546132</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6960333</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859204</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136859206</v>
+      </c>
+      <c r="B26" t="n">
+        <v>104876</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>546126</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6960333</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859206</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136859213</v>
+      </c>
+      <c r="B27" t="n">
+        <v>104876</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>545999</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6960308</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859213</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128369928</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>546105</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6960345</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369928</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128369930</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gustavsnäs, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>546104</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6960332</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128369930</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136859202</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101465</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mörtsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>546132</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6960342</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136859202</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>104000117</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Storflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>545939</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6960325</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>Via Johan Staaf</t>
         </is>
       </c>
-      <c r="AY19" t="inlineStr">
+      <c r="AY31" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
+      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104000117</t>
         </is>
@@ -2675,6 +4037,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136859212</v>
       </c>
       <c r="B4" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>96565</v>
+        <v>96571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136859207</v>
       </c>
       <c r="B10" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136859208</v>
       </c>
       <c r="B11" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136859209</v>
       </c>
       <c r="B12" t="n">
-        <v>93083</v>
+        <v>93085</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104876</v>
+        <v>104882</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136859202</v>
       </c>
       <c r="B30" t="n">
-        <v>101465</v>
+        <v>101471</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136859212</v>
       </c>
       <c r="B4" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>96571</v>
+        <v>96573</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136859207</v>
       </c>
       <c r="B10" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136859208</v>
       </c>
       <c r="B11" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136859209</v>
       </c>
       <c r="B12" t="n">
-        <v>93085</v>
+        <v>93087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104882</v>
+        <v>104884</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136859202</v>
       </c>
       <c r="B30" t="n">
-        <v>101471</v>
+        <v>101473</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136859212</v>
       </c>
       <c r="B4" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>96573</v>
+        <v>96574</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136859207</v>
       </c>
       <c r="B10" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136859208</v>
       </c>
       <c r="B11" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136859209</v>
       </c>
       <c r="B12" t="n">
-        <v>93087</v>
+        <v>93088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104884</v>
+        <v>104885</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136859202</v>
       </c>
       <c r="B30" t="n">
-        <v>101473</v>
+        <v>101474</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136859212</v>
       </c>
       <c r="B4" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136859207</v>
       </c>
       <c r="B10" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136859208</v>
       </c>
       <c r="B11" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136859209</v>
       </c>
       <c r="B12" t="n">
-        <v>93088</v>
+        <v>93094</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104885</v>
+        <v>104891</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136859202</v>
       </c>
       <c r="B30" t="n">
-        <v>101474</v>
+        <v>101480</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136859212</v>
       </c>
       <c r="B4" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136859207</v>
       </c>
       <c r="B10" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136859208</v>
       </c>
       <c r="B11" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136859209</v>
       </c>
       <c r="B12" t="n">
-        <v>93094</v>
+        <v>93098</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104891</v>
+        <v>104895</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136859202</v>
       </c>
       <c r="B30" t="n">
-        <v>101480</v>
+        <v>101484</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -1132,7 +1132,7 @@
         <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104895</v>
+        <v>104897</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136859202</v>
       </c>
       <c r="B30" t="n">
-        <v>101484</v>
+        <v>101486</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136859212</v>
       </c>
       <c r="B4" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136859207</v>
       </c>
       <c r="B10" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136859208</v>
       </c>
       <c r="B11" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136859209</v>
       </c>
       <c r="B12" t="n">
-        <v>93098</v>
+        <v>93100</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104897</v>
+        <v>104899</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136859202</v>
       </c>
       <c r="B30" t="n">
-        <v>101486</v>
+        <v>101488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136859212</v>
       </c>
       <c r="B4" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136859207</v>
       </c>
       <c r="B10" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136859208</v>
       </c>
       <c r="B11" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136859209</v>
       </c>
       <c r="B12" t="n">
-        <v>93100</v>
+        <v>93113</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104899</v>
+        <v>104912</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136859202</v>
       </c>
       <c r="B30" t="n">
-        <v>101488</v>
+        <v>101501</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136859212</v>
       </c>
       <c r="B4" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136859207</v>
       </c>
       <c r="B10" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136859208</v>
       </c>
       <c r="B11" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136859209</v>
       </c>
       <c r="B12" t="n">
-        <v>93113</v>
+        <v>93115</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104912</v>
+        <v>104914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136859202</v>
       </c>
       <c r="B30" t="n">
-        <v>101501</v>
+        <v>101503</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136859212</v>
       </c>
       <c r="B4" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136859207</v>
       </c>
       <c r="B10" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136859208</v>
       </c>
       <c r="B11" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136859209</v>
       </c>
       <c r="B12" t="n">
-        <v>93115</v>
+        <v>93118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104914</v>
+        <v>104917</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136859202</v>
       </c>
       <c r="B30" t="n">
-        <v>101503</v>
+        <v>101506</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136859212</v>
       </c>
       <c r="B4" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136859207</v>
       </c>
       <c r="B10" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136859208</v>
       </c>
       <c r="B11" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136859209</v>
       </c>
       <c r="B12" t="n">
-        <v>93118</v>
+        <v>93128</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104917</v>
+        <v>104936</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136859202</v>
       </c>
       <c r="B30" t="n">
-        <v>101506</v>
+        <v>101521</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136859212</v>
       </c>
       <c r="B4" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136859207</v>
       </c>
       <c r="B10" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136859208</v>
       </c>
       <c r="B11" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136859209</v>
       </c>
       <c r="B12" t="n">
-        <v>93128</v>
+        <v>93129</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104936</v>
+        <v>104937</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136859202</v>
       </c>
       <c r="B30" t="n">
-        <v>101521</v>
+        <v>101522</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136859212</v>
       </c>
       <c r="B4" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136859207</v>
       </c>
       <c r="B10" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136859208</v>
       </c>
       <c r="B11" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136859209</v>
       </c>
       <c r="B12" t="n">
-        <v>93129</v>
+        <v>93132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104937</v>
+        <v>104942</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136859202</v>
       </c>
       <c r="B30" t="n">
-        <v>101522</v>
+        <v>101527</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136859212</v>
       </c>
       <c r="B4" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136859207</v>
       </c>
       <c r="B10" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136859208</v>
       </c>
       <c r="B11" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136859209</v>
       </c>
       <c r="B12" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104942</v>
+        <v>104945</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136859202</v>
       </c>
       <c r="B30" t="n">
-        <v>101527</v>
+        <v>101530</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136859212</v>
       </c>
       <c r="B4" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136859207</v>
       </c>
       <c r="B10" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136859208</v>
       </c>
       <c r="B11" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136859209</v>
       </c>
       <c r="B12" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104945</v>
+        <v>104951</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136859202</v>
       </c>
       <c r="B30" t="n">
-        <v>101530</v>
+        <v>101536</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104951</v>
+        <v>104952</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 49712-2024 artfynd.xlsx
+++ b/artfynd/A 49712-2024 artfynd.xlsx
@@ -899,7 +899,7 @@
         <v>136859212</v>
       </c>
       <c r="B4" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
         <v>136859203</v>
       </c>
       <c r="B6" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         <v>136859207</v>
       </c>
       <c r="B10" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>136859208</v>
       </c>
       <c r="B11" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>136859209</v>
       </c>
       <c r="B12" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>136859201</v>
       </c>
       <c r="B16" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         <v>136859211</v>
       </c>
       <c r="B18" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136859214</v>
       </c>
       <c r="B19" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>136859204</v>
       </c>
       <c r="B25" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>136859206</v>
       </c>
       <c r="B26" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>136859213</v>
       </c>
       <c r="B27" t="n">
-        <v>104952</v>
+        <v>104964</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>136859202</v>
       </c>
       <c r="B30" t="n">
-        <v>101536</v>
+        <v>101548</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
